--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792253</v>
+        <v>121792607</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -721,14 +721,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348514</v>
+        <v>348455</v>
       </c>
       <c r="R2" t="n">
-        <v>6519160</v>
+        <v>6519346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792607</v>
+        <v>121791871</v>
       </c>
       <c r="B3" t="n">
         <v>100379</v>
@@ -838,14 +838,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348455</v>
+        <v>348561</v>
       </c>
       <c r="R3" t="n">
-        <v>6519346</v>
+        <v>6519216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792568</v>
+        <v>121792399</v>
       </c>
       <c r="B4" t="n">
         <v>100379</v>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348486</v>
+        <v>348481</v>
       </c>
       <c r="R4" t="n">
-        <v>6519336</v>
+        <v>6519252</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121792318</v>
+        <v>121792063</v>
       </c>
       <c r="B5" t="n">
         <v>100379</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>348459</v>
+        <v>348553</v>
       </c>
       <c r="R5" t="n">
-        <v>6519139</v>
+        <v>6519199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121792399</v>
+        <v>121792253</v>
       </c>
       <c r="B6" t="n">
         <v>100379</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348481</v>
+        <v>348514</v>
       </c>
       <c r="R6" t="n">
-        <v>6519252</v>
+        <v>6519160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121791871</v>
+        <v>121792568</v>
       </c>
       <c r="B7" t="n">
         <v>100379</v>
@@ -1306,14 +1306,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>348561</v>
+        <v>348486</v>
       </c>
       <c r="R7" t="n">
-        <v>6519216</v>
+        <v>6519336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121792063</v>
+        <v>121792318</v>
       </c>
       <c r="B8" t="n">
         <v>100379</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>348553</v>
+        <v>348459</v>
       </c>
       <c r="R8" t="n">
-        <v>6519199</v>
+        <v>6519139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792607</v>
+        <v>121791871</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -721,14 +721,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348455</v>
+        <v>348561</v>
       </c>
       <c r="R2" t="n">
-        <v>6519346</v>
+        <v>6519216</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121791871</v>
+        <v>121792063</v>
       </c>
       <c r="B3" t="n">
         <v>100379</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348561</v>
+        <v>348553</v>
       </c>
       <c r="R3" t="n">
-        <v>6519216</v>
+        <v>6519199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792399</v>
+        <v>121792253</v>
       </c>
       <c r="B4" t="n">
         <v>100379</v>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348481</v>
+        <v>348514</v>
       </c>
       <c r="R4" t="n">
-        <v>6519252</v>
+        <v>6519160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121792063</v>
+        <v>121792568</v>
       </c>
       <c r="B5" t="n">
         <v>100379</v>
@@ -1072,14 +1072,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>348553</v>
+        <v>348486</v>
       </c>
       <c r="R5" t="n">
-        <v>6519199</v>
+        <v>6519336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121792253</v>
+        <v>121792607</v>
       </c>
       <c r="B6" t="n">
         <v>100379</v>
@@ -1189,14 +1189,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348514</v>
+        <v>348455</v>
       </c>
       <c r="R6" t="n">
-        <v>6519160</v>
+        <v>6519346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121792568</v>
+        <v>121792318</v>
       </c>
       <c r="B7" t="n">
         <v>100379</v>
@@ -1306,14 +1306,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>348486</v>
+        <v>348459</v>
       </c>
       <c r="R7" t="n">
-        <v>6519336</v>
+        <v>6519139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121792318</v>
+        <v>121792399</v>
       </c>
       <c r="B8" t="n">
         <v>100379</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>348459</v>
+        <v>348481</v>
       </c>
       <c r="R8" t="n">
-        <v>6519139</v>
+        <v>6519252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,1376 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132335166</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, vid Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>348580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6519243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Murken granstam.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132335807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>348516</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6519293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>På ek.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132336006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132335439</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96430</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>348505</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6519139</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132335808</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>348481</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6519286</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132335525</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>348462</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6519162</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132336196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>348529</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6519171</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132336000</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96409</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132335150</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>348505</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6519139</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132335997</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95916</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blek stjärnmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mnium stellare</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132335167</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>210</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, vid Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>348595</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6519199</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Murken granstuppe.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132335999</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96203</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132336478</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>348493</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6519126</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B12" t="n">
-        <v>96430</v>
+        <v>101296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R12" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,16 +1895,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1921,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101296</v>
+        <v>96430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,34 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,6 +1992,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>101296</v>
+        <v>96409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R15" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>96409</v>
+        <v>101296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R16" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96398</v>
+        <v>96403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>101296</v>
+        <v>96435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R12" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1895,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1911,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96430</v>
+        <v>101301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,34 +1932,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,16 +2002,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2130,7 +2130,7 @@
         <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>96409</v>
+        <v>96414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95916</v>
+        <v>95921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96203</v>
+        <v>96208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,6 +2861,210 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132397690</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132397692</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96163</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>101301</v>
+        <v>96438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R12" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1895,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1911,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96435</v>
+        <v>101304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,34 +1932,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,16 +2002,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2130,7 +2130,7 @@
         <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>96414</v>
+        <v>96417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95921</v>
+        <v>95924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96208</v>
+        <v>96211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>132397690</v>
       </c>
       <c r="B22" t="n">
-        <v>97788</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>132397692</v>
       </c>
       <c r="B23" t="n">
-        <v>96163</v>
+        <v>96166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,6 +3065,879 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132446047</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6519264</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132446046</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>348506</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6519266</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132446045</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96211</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>348545</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6519237</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132446053</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111368</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>348463</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6519366</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132446044</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96417</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>348545</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6519237</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132446050</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>348486</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6519319</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132446043</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>348552</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6519205</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132446048</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>348482</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6519312</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B12" t="n">
-        <v>96438</v>
+        <v>101304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R12" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,16 +1895,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1921,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101304</v>
+        <v>96438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,34 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,6 +1992,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>101304</v>
+        <v>96438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R12" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1895,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1911,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96438</v>
+        <v>101304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,34 +1932,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,16 +2002,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -3165,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B25" t="n">
-        <v>101304</v>
+        <v>96211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R25" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B26" t="n">
-        <v>96211</v>
+        <v>101304</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R26" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446048</v>
+        <v>132446052</v>
       </c>
       <c r="B31" t="n">
-        <v>96406</v>
+        <v>101304</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,34 +3758,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R31" t="n">
-        <v>6519312</v>
+        <v>6519355</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446052</v>
+        <v>132446048</v>
       </c>
       <c r="B32" t="n">
-        <v>101304</v>
+        <v>96406</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3855,34 +3855,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348480</v>
+        <v>348482</v>
       </c>
       <c r="R32" t="n">
-        <v>6519355</v>
+        <v>6519312</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>96438</v>
+        <v>96446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>132335525</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95924</v>
+        <v>95932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>132397690</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>97799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>132397692</v>
       </c>
       <c r="B23" t="n">
-        <v>96166</v>
+        <v>96174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>132446047</v>
       </c>
       <c r="B24" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>132446045</v>
       </c>
       <c r="B25" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>132446046</v>
       </c>
       <c r="B26" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>132446053</v>
       </c>
       <c r="B27" t="n">
-        <v>111368</v>
+        <v>111376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>132446044</v>
       </c>
       <c r="B28" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>132446050</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>132446043</v>
       </c>
       <c r="B30" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446052</v>
+        <v>132446048</v>
       </c>
       <c r="B31" t="n">
-        <v>101304</v>
+        <v>96414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,34 +3758,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348480</v>
+        <v>348482</v>
       </c>
       <c r="R31" t="n">
-        <v>6519355</v>
+        <v>6519312</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446048</v>
+        <v>132446052</v>
       </c>
       <c r="B32" t="n">
-        <v>96406</v>
+        <v>101312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3855,34 +3855,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R32" t="n">
-        <v>6519312</v>
+        <v>6519355</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B12" t="n">
-        <v>96446</v>
+        <v>101312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R12" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,16 +1895,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1921,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101312</v>
+        <v>96446</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,34 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,6 +1992,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B15" t="n">
-        <v>96425</v>
+        <v>101312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R15" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>101312</v>
+        <v>96425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B25" t="n">
-        <v>96219</v>
+        <v>101312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R25" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B26" t="n">
-        <v>101312</v>
+        <v>96219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R26" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>132335808</v>
       </c>
       <c r="B12" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>132335525</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>101312</v>
+        <v>96435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R15" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>96425</v>
+        <v>101323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R16" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95932</v>
+        <v>95942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96219</v>
+        <v>96229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>132397690</v>
       </c>
       <c r="B22" t="n">
-        <v>97799</v>
+        <v>97809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>132397692</v>
       </c>
       <c r="B23" t="n">
-        <v>96174</v>
+        <v>96184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>132446047</v>
       </c>
       <c r="B24" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B25" t="n">
-        <v>101312</v>
+        <v>96229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R25" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B26" t="n">
-        <v>96219</v>
+        <v>101323</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R26" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3362,7 +3362,7 @@
         <v>132446053</v>
       </c>
       <c r="B27" t="n">
-        <v>111376</v>
+        <v>111387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>132446044</v>
       </c>
       <c r="B28" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>132446050</v>
       </c>
       <c r="B29" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>132446043</v>
       </c>
       <c r="B30" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446048</v>
+        <v>132446052</v>
       </c>
       <c r="B31" t="n">
-        <v>96414</v>
+        <v>101323</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,34 +3758,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R31" t="n">
-        <v>6519312</v>
+        <v>6519355</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446052</v>
+        <v>132446048</v>
       </c>
       <c r="B32" t="n">
-        <v>101312</v>
+        <v>96424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3855,34 +3855,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348480</v>
+        <v>348482</v>
       </c>
       <c r="R32" t="n">
-        <v>6519355</v>
+        <v>6519312</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>101323</v>
+        <v>96457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1825,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R12" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1895,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1911,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96456</v>
+        <v>101324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,34 +1932,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,16 +2002,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2130,7 +2130,7 @@
         <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95942</v>
+        <v>95943</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96229</v>
+        <v>96230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>132397690</v>
       </c>
       <c r="B22" t="n">
-        <v>97809</v>
+        <v>97810</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>132397692</v>
       </c>
       <c r="B23" t="n">
-        <v>96184</v>
+        <v>96185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>132446047</v>
       </c>
       <c r="B24" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>132446045</v>
       </c>
       <c r="B25" t="n">
-        <v>96229</v>
+        <v>96230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>132446046</v>
       </c>
       <c r="B26" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>132446053</v>
       </c>
       <c r="B27" t="n">
-        <v>111387</v>
+        <v>111388</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>132446044</v>
       </c>
       <c r="B28" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>132446050</v>
       </c>
       <c r="B29" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>132446043</v>
       </c>
       <c r="B30" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>132446052</v>
       </c>
       <c r="B31" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>132446048</v>
       </c>
       <c r="B32" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335807</v>
       </c>
       <c r="B10" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>132336006</v>
       </c>
       <c r="B11" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>132335439</v>
       </c>
       <c r="B12" t="n">
-        <v>96457</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B15" t="n">
-        <v>96436</v>
+        <v>101325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R15" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>101324</v>
+        <v>96437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
         <v>132335150</v>
       </c>
       <c r="B17" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335997</v>
       </c>
       <c r="B18" t="n">
-        <v>95943</v>
+        <v>95944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335167</v>
       </c>
       <c r="B19" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335999</v>
       </c>
       <c r="B20" t="n">
-        <v>96230</v>
+        <v>96231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132336478</v>
       </c>
       <c r="B21" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>132397690</v>
       </c>
       <c r="B22" t="n">
-        <v>97810</v>
+        <v>97811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>132397692</v>
       </c>
       <c r="B23" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>132446047</v>
       </c>
       <c r="B24" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>132446045</v>
       </c>
       <c r="B25" t="n">
-        <v>96230</v>
+        <v>96231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>132446046</v>
       </c>
       <c r="B26" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>132446053</v>
       </c>
       <c r="B27" t="n">
-        <v>111388</v>
+        <v>111389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>132446044</v>
       </c>
       <c r="B28" t="n">
-        <v>96436</v>
+        <v>96437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>132446050</v>
       </c>
       <c r="B29" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>132446043</v>
       </c>
       <c r="B30" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446052</v>
+        <v>132446048</v>
       </c>
       <c r="B31" t="n">
-        <v>101324</v>
+        <v>96426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,34 +3758,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348480</v>
+        <v>348482</v>
       </c>
       <c r="R31" t="n">
-        <v>6519355</v>
+        <v>6519312</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446048</v>
+        <v>132446052</v>
       </c>
       <c r="B32" t="n">
-        <v>96425</v>
+        <v>101325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3855,34 +3855,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R32" t="n">
-        <v>6519312</v>
+        <v>6519355</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B15" t="n">
-        <v>101325</v>
+        <v>96437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R15" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>96437</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R16" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335166</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335167</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446044</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335807</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446043</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397692</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335999</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446045</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2336,6 +2416,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335439</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2445,6 +2530,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335525</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2562,6 +2652,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446029</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2659,6 +2754,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446053</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2771,6 +2871,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791871</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792063</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792253</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792318</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792399</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3331,6 +3456,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792568</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3443,6 +3573,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792607</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335808</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3642,6 +3782,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336006</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3744,6 +3889,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336196</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3841,6 +3991,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336478</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3938,6 +4093,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446046</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4035,6 +4195,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4132,6 +4297,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4234,8 +4404,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336005</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,10 +2424,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335525</v>
+        <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>96628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,49 +2435,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348462</v>
+        <v>348719</v>
       </c>
       <c r="R18" t="n">
-        <v>6519162</v>
+        <v>6519093</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2501,12 +2489,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,74 +2505,96 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446029</v>
+        <v>132335525</v>
       </c>
       <c r="B19" t="n">
-        <v>8374</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106540</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348623</v>
+        <v>348462</v>
       </c>
       <c r="R19" t="n">
-        <v>6519241</v>
+        <v>6519162</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,12 +2618,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,46 +2634,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446053</v>
+        <v>132446029</v>
       </c>
       <c r="B20" t="n">
-        <v>111471</v>
+        <v>8374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2671,34 +2666,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348463</v>
+        <v>348623</v>
       </c>
       <c r="R20" t="n">
-        <v>6519366</v>
+        <v>6519241</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,6 +2742,21 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2756,64 +2771,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121791871</v>
+        <v>132446053</v>
       </c>
       <c r="B21" t="n">
-        <v>101326</v>
+        <v>111471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348561</v>
+        <v>348463</v>
       </c>
       <c r="R21" t="n">
-        <v>6519216</v>
+        <v>6519366</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2837,12 +2842,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,84 +2858,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121792063</v>
+        <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>101326</v>
+        <v>111586</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348553</v>
+        <v>348618</v>
       </c>
       <c r="R22" t="n">
-        <v>6519199</v>
+        <v>6519260</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2954,12 +2944,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,33 +2960,28 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121792253</v>
+        <v>121791871</v>
       </c>
       <c r="B23" t="n">
         <v>101326</v>
@@ -3041,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348514</v>
+        <v>348561</v>
       </c>
       <c r="R23" t="n">
-        <v>6519160</v>
+        <v>6519216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3090,7 +3075,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3107,13 +3092,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121792318</v>
+        <v>121792063</v>
       </c>
       <c r="B24" t="n">
         <v>101326</v>
@@ -3158,10 +3143,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348459</v>
+        <v>348553</v>
       </c>
       <c r="R24" t="n">
-        <v>6519139</v>
+        <v>6519199</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,7 +3192,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3224,13 +3209,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121792399</v>
+        <v>121792253</v>
       </c>
       <c r="B25" t="n">
         <v>101326</v>
@@ -3275,10 +3260,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348481</v>
+        <v>348514</v>
       </c>
       <c r="R25" t="n">
-        <v>6519252</v>
+        <v>6519160</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3324,7 +3309,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3341,13 +3326,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121792568</v>
+        <v>121792318</v>
       </c>
       <c r="B26" t="n">
         <v>101326</v>
@@ -3388,14 +3373,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348486</v>
+        <v>348459</v>
       </c>
       <c r="R26" t="n">
-        <v>6519336</v>
+        <v>6519139</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,13 +3443,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121792607</v>
+        <v>121792399</v>
       </c>
       <c r="B27" t="n">
         <v>101326</v>
@@ -3505,14 +3490,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348455</v>
+        <v>348481</v>
       </c>
       <c r="R27" t="n">
-        <v>6519346</v>
+        <v>6519252</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,7 +3543,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3575,16 +3560,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132335808</v>
+        <v>121792568</v>
       </c>
       <c r="B28" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3610,16 +3595,26 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348481</v>
+        <v>348486</v>
       </c>
       <c r="R28" t="n">
-        <v>6519286</v>
+        <v>6519336</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3646,12 +3641,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3662,31 +3657,36 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132336006</v>
+        <v>121792607</v>
       </c>
       <c r="B29" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,16 +3712,26 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348550</v>
+        <v>348455</v>
       </c>
       <c r="R29" t="n">
-        <v>6519223</v>
+        <v>6519346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,12 +3758,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3765,32 +3775,32 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132336196</v>
+        <v>132335808</v>
       </c>
       <c r="B30" t="n">
         <v>101403</v>
@@ -3821,14 +3831,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348529</v>
+        <v>348481</v>
       </c>
       <c r="R30" t="n">
-        <v>6519171</v>
+        <v>6519286</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3872,11 +3882,6 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3891,13 +3896,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132336478</v>
+        <v>132336006</v>
       </c>
       <c r="B31" t="n">
         <v>101403</v>
@@ -3932,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348493</v>
+        <v>348550</v>
       </c>
       <c r="R31" t="n">
-        <v>6519126</v>
+        <v>6519223</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3979,6 +3984,11 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -3993,13 +4003,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446046</v>
+        <v>132336196</v>
       </c>
       <c r="B32" t="n">
         <v>101403</v>
@@ -4030,17 +4040,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348506</v>
+        <v>348529</v>
       </c>
       <c r="R32" t="n">
-        <v>6519266</v>
+        <v>6519171</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4064,12 +4074,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,28 +4090,33 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/132336196</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132446050</v>
+        <v>132336478</v>
       </c>
       <c r="B33" t="n">
         <v>101403</v>
@@ -4132,17 +4147,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348486</v>
+        <v>348493</v>
       </c>
       <c r="R33" t="n">
-        <v>6519319</v>
+        <v>6519126</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,12 +4181,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,24 +4201,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/132336478</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446052</v>
+        <v>132446046</v>
       </c>
       <c r="B34" t="n">
         <v>101403</v>
@@ -4234,14 +4249,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348480</v>
+        <v>348506</v>
       </c>
       <c r="R34" t="n">
-        <v>6519355</v>
+        <v>6519266</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4299,16 +4314,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132446046</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132336005</v>
+        <v>132446050</v>
       </c>
       <c r="B35" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,37 +4331,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348550</v>
+        <v>348486</v>
       </c>
       <c r="R35" t="n">
-        <v>6519223</v>
+        <v>6519319</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4370,12 +4385,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4386,25 +4401,229 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132336005</t>
         </is>
@@ -4446,6 +4665,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
